--- a/public/downloads/Park2D2019.xlsx
+++ b/public/downloads/Park2D2019.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>OH</t>
   </si>
   <si>
     <t>OOH</t>
-  </si>
-  <si>
-    <t>O</t>
   </si>
 </sst>
 </file>
@@ -643,9 +666,7 @@
       <c r="H3" s="4">
         <v>1.951122603020243</v>
       </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
+      <c r="I3" s="4"/>
       <c r="J3" s="4">
         <v>2.235760901902621</v>
       </c>
@@ -659,10 +680,10 @@
         <v>9</v>
       </c>
       <c r="N3" s="5">
-        <v>57.90870523452759</v>
+        <v>57908.70523452759</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03275379255346583</v>
+        <v>32.75379255346584</v>
       </c>
       <c r="P3" s="5">
         <v>1768</v>
@@ -709,10 +730,10 @@
         <v>9</v>
       </c>
       <c r="N4" s="5">
-        <v>66.07630968093872</v>
+        <v>66076.30968093872</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04437629931560693</v>
+        <v>44.37629931560693</v>
       </c>
       <c r="P4" s="5">
         <v>1489</v>
@@ -759,10 +780,10 @@
         <v>9</v>
       </c>
       <c r="N5" s="5">
-        <v>365.0875473022461</v>
+        <v>365087.5473022461</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1895573973531911</v>
+        <v>189.5573973531911</v>
       </c>
       <c r="P5" s="5">
         <v>1926</v>
@@ -809,10 +830,10 @@
         <v>9</v>
       </c>
       <c r="N6" s="5">
-        <v>135.2281744480133</v>
+        <v>135228.1744480133</v>
       </c>
       <c r="O6" s="4">
-        <v>0.0912470812739631</v>
+        <v>91.24708127396309</v>
       </c>
       <c r="P6" s="5">
         <v>1482</v>
@@ -859,10 +880,10 @@
         <v>9</v>
       </c>
       <c r="N7" s="5">
-        <v>896.4930973052979</v>
+        <v>896493.0973052979</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1527245480928957</v>
+        <v>152.7245480928957</v>
       </c>
       <c r="P7" s="5">
         <v>5870</v>
@@ -909,10 +930,10 @@
         <v>9</v>
       </c>
       <c r="N8" s="5">
-        <v>16.84098029136658</v>
+        <v>16840.98029136658</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01176867944889349</v>
+        <v>11.76867944889348</v>
       </c>
       <c r="P8" s="5">
         <v>1431</v>
@@ -959,10 +980,10 @@
         <v>9</v>
       </c>
       <c r="N9" s="5">
-        <v>37.33588838577271</v>
+        <v>37335.88838577271</v>
       </c>
       <c r="O9" s="4">
-        <v>0.0280932192518982</v>
+        <v>28.0932192518982</v>
       </c>
       <c r="P9" s="5">
         <v>1329</v>
@@ -1009,10 +1030,10 @@
         <v>9</v>
       </c>
       <c r="N10" s="5">
-        <v>106.7783935070038</v>
+        <v>106778.3935070038</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08316074260670077</v>
+        <v>83.16074260670077</v>
       </c>
       <c r="P10" s="5">
         <v>1284</v>
@@ -1043,9 +1064,7 @@
       <c r="H11" s="4">
         <v>2.07090570303909</v>
       </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
+      <c r="I11" s="4"/>
       <c r="J11" s="4">
         <v>2.293910573983643</v>
       </c>
@@ -1059,10 +1078,10 @@
         <v>9</v>
       </c>
       <c r="N11" s="5">
-        <v>59.59914112091064</v>
+        <v>59599.14112091064</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03667639453594501</v>
+        <v>36.67639453594501</v>
       </c>
       <c r="P11" s="5">
         <v>1625</v>
@@ -1109,10 +1128,10 @@
         <v>9</v>
       </c>
       <c r="N12" s="5">
-        <v>21.84954833984375</v>
+        <v>21849.54833984375</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01666632215091057</v>
+        <v>16.66632215091057</v>
       </c>
       <c r="P12" s="5">
         <v>1311</v>
@@ -1159,10 +1178,10 @@
         <v>9</v>
       </c>
       <c r="N13" s="5">
-        <v>280.634331703186</v>
+        <v>280634.331703186</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07230979945972328</v>
+        <v>72.30979945972328</v>
       </c>
       <c r="P13" s="5">
         <v>3881</v>
@@ -1209,10 +1228,10 @@
         <v>9</v>
       </c>
       <c r="N14" s="5">
-        <v>124.8828270435333</v>
+        <v>124882.8270435333</v>
       </c>
       <c r="O14" s="4">
-        <v>0.1936167861140052</v>
+        <v>193.6167861140052</v>
       </c>
       <c r="P14" s="5">
         <v>645</v>
@@ -1259,10 +1278,10 @@
         <v>9</v>
       </c>
       <c r="N15" s="5">
-        <v>254.1782402992249</v>
+        <v>254178.2402992249</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2081721869772521</v>
+        <v>208.1721869772521</v>
       </c>
       <c r="P15" s="5">
         <v>1221</v>
@@ -1309,10 +1328,10 @@
         <v>9</v>
       </c>
       <c r="N16" s="5">
-        <v>88.96375370025635</v>
+        <v>88963.75370025635</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1069275885820389</v>
+        <v>106.9275885820389</v>
       </c>
       <c r="P16" s="5">
         <v>832</v>
@@ -1359,10 +1378,10 @@
         <v>9</v>
       </c>
       <c r="N17" s="5">
-        <v>202.5837965011597</v>
+        <v>202583.7965011597</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1007879584582884</v>
+        <v>100.7879584582884</v>
       </c>
       <c r="P17" s="5">
         <v>2010</v>
@@ -1390,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1420,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1462,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,66 +1493,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1583478608957734</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2674314961829318</v>
-      </c>
+        <v>1.698037691272716</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.1977275260267639</v>
+        <v>1.837639008938353</v>
       </c>
       <c r="E3" s="4">
-        <v>69.21768707482957</v>
+        <v>75.78231292516972</v>
       </c>
       <c r="F3" s="4">
-        <v>75.40268456375873</v>
+        <v>72.10290827740373</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.698037691272716</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2202654849078757</v>
+        <v>1.02878011010098</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2957029764756047</v>
+        <v>1.466535642661007</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1958764805869778</v>
+        <v>1.127230708956526</v>
       </c>
       <c r="E4" s="4">
-        <v>85.8843537414967</v>
+        <v>81.83673469387746</v>
       </c>
       <c r="F4" s="4">
-        <v>87.59507829977632</v>
+        <v>84.79865771812113</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -1542,37 +1605,51 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.02878011010098</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.466535642661007</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3762313865845084</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4651857425105366</v>
-      </c>
+        <v>1.133222497243205</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.3533522622446981</v>
+        <v>1.865614513915699</v>
       </c>
       <c r="E5" s="4">
-        <v>85.78231292517017</v>
+        <v>67.89115646258459</v>
       </c>
       <c r="F5" s="4">
-        <v>87.02460850111846</v>
+        <v>66.84563758389211</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -1581,11 +1658,25 @@
         <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.133222497243205</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1687,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1706,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1748,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,75 +1779,109 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.448847377635199</v>
+        <v>0.9097461237821941</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.9097461237821941</v>
       </c>
       <c r="D3" s="4">
-        <v>1.792310321665961</v>
+        <v>0.9132047826363608</v>
       </c>
       <c r="E3" s="4">
-        <v>67.34693877551003</v>
+        <v>83.36734693877551</v>
       </c>
       <c r="F3" s="4">
-        <v>67.71812080536955</v>
+        <v>88.25503355704694</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9097461237821941</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9097461237821941</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>2.05030283870777</v>
+        <v>0.5019201782815799</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.5461023853658844</v>
       </c>
       <c r="D4" s="4">
-        <v>2.321377133751715</v>
+        <v>0.6223730591409549</v>
       </c>
       <c r="E4" s="4">
-        <v>75.71428571428582</v>
+        <v>84.08163265306128</v>
       </c>
       <c r="F4" s="4">
-        <v>69.13497390007456</v>
+        <v>84.89932885906029</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>1</v>
@@ -1755,50 +1895,82 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5019201782815799</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5461023853658844</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.7135668927743</v>
+        <v>0.9089950873700824</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.8595380671213206</v>
       </c>
       <c r="D5" s="4">
-        <v>2.768044266533252</v>
+        <v>1.011625702604457</v>
       </c>
       <c r="E5" s="4">
-        <v>71.12244897959134</v>
+        <v>76.25850340136061</v>
       </c>
       <c r="F5" s="4">
-        <v>70.11185682326507</v>
+        <v>73.926174496643</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9089950873700824</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8595380671213206</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +1981,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2000,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2042,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,25 +2073,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6422553105524761</v>
+        <v>0.3762313865845084</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8551824980113452</v>
+        <v>0.4651857425105366</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7299339019627951</v>
+        <v>0.3533522622446981</v>
       </c>
       <c r="E3" s="4">
-        <v>82.55102040816327</v>
+        <v>85.78231292517017</v>
       </c>
       <c r="F3" s="4">
-        <v>84.35495898583171</v>
+        <v>87.02460850111846</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
@@ -1927,34 +2132,50 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3762313865845084</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4651857425105366</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.549340693854901</v>
+        <v>0.1583478608957734</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.2674314961829318</v>
       </c>
       <c r="D4" s="4">
-        <v>2.323272958819871</v>
+        <v>0.1977275260267639</v>
       </c>
       <c r="E4" s="4">
-        <v>72.0181405895692</v>
+        <v>69.21768707482957</v>
       </c>
       <c r="F4" s="4">
-        <v>63.90007457121474</v>
+        <v>75.40268456375873</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>2</v>
@@ -1963,30 +2184,46 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1583478608957734</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2674314961829318</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9614200129423504</v>
+        <v>0.2202654849078757</v>
       </c>
       <c r="C5" s="4">
-        <v>1.219000563556619</v>
+        <v>0.2957029764756047</v>
       </c>
       <c r="D5" s="4">
-        <v>1.070462498497363</v>
+        <v>0.1958764805869778</v>
       </c>
       <c r="E5" s="4">
-        <v>83.39002267573694</v>
+        <v>85.8843537414967</v>
       </c>
       <c r="F5" s="4">
-        <v>81.40566741237896</v>
+        <v>87.59507829977632</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -2009,9 +2246,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2202654849078757</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2957029764756047</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2275,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2283,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2294,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2336,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,66 +2367,94 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.079698169566351</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1511855864373501</v>
-      </c>
+        <v>2.7135668927743</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>1.706762238678493</v>
+        <v>2.768044266533252</v>
       </c>
       <c r="E3" s="4">
-        <v>75.27210884353811</v>
+        <v>71.12244897959134</v>
       </c>
       <c r="F3" s="4">
-        <v>68.3557046979859</v>
+        <v>70.11185682326507</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.7135668927743</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.211753542646572</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>1.448847377635199</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>2.460427299563889</v>
+        <v>1.792310321665961</v>
       </c>
       <c r="E4" s="4">
-        <v>67.24489795918318</v>
+        <v>67.34693877551003</v>
       </c>
       <c r="F4" s="4">
-        <v>59.08277404921667</v>
+        <v>67.71812080536955</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -2167,39 +2463,51 @@
         <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.448847377635199</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.002951490165287</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>2.05030283870777</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>2.111675693026579</v>
+        <v>2.321377133751715</v>
       </c>
       <c r="E5" s="4">
-        <v>75.44217687074811</v>
+        <v>75.71428571428582</v>
       </c>
       <c r="F5" s="4">
-        <v>66.25279642058011</v>
+        <v>69.13497390007456</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -2208,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -2220,11 +2528,25 @@
         <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.05030283870777</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2557,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2565,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2576,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2618,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,66 +2649,100 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1790981382473455</v>
+        <v>0.9614200129423504</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1790981382473455</v>
+        <v>1.219000563556619</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1648009807213766</v>
+        <v>1.070462498497363</v>
       </c>
       <c r="E3" s="4">
-        <v>97.27891156462584</v>
+        <v>83.39002267573694</v>
       </c>
       <c r="F3" s="4">
-        <v>96.8903803131991</v>
+        <v>81.40566741237896</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9614200129423504</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.219000563556619</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1353772883012656</v>
+        <v>0.6422553105524761</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1394850668312415</v>
+        <v>0.8551824980113452</v>
       </c>
       <c r="D4" s="4">
-        <v>0.08902871652385554</v>
+        <v>0.7299339019627951</v>
       </c>
       <c r="E4" s="4">
-        <v>94.65986394557821</v>
+        <v>82.55102040816327</v>
       </c>
       <c r="F4" s="4">
-        <v>91.31991051454159</v>
+        <v>84.35495898583171</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -2394,50 +2765,78 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6422553105524761</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8551824980113452</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2507433826043168</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2507433826043168</v>
-      </c>
+        <v>1.549340693854901</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.2440630132272374</v>
+        <v>2.323272958819871</v>
       </c>
       <c r="E5" s="4">
-        <v>97.65306122448979</v>
+        <v>72.0181405895692</v>
       </c>
       <c r="F5" s="4">
-        <v>97.76286353467563</v>
+        <v>63.90007457121474</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.549340693854901</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2847,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2855,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2866,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2908,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,66 +2939,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.399449711295644</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.399449711295644</v>
-      </c>
+        <v>2.002951490165287</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.3886784963336574</v>
+        <v>2.111675693026579</v>
       </c>
       <c r="E3" s="4">
-        <v>98.57142857142857</v>
+        <v>75.44217687074811</v>
       </c>
       <c r="F3" s="4">
-        <v>97.93064876957496</v>
+        <v>66.25279642058011</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.002951490165287</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3432535632843283</v>
+        <v>1.079698169566351</v>
       </c>
       <c r="C4" s="4">
-        <v>0.179299953186316</v>
+        <v>0.1511855864373501</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7333429162099657</v>
+        <v>1.706762238678493</v>
       </c>
       <c r="E4" s="4">
-        <v>83.2879818594114</v>
+        <v>75.27210884353811</v>
       </c>
       <c r="F4" s="4">
-        <v>76.2080536912743</v>
+        <v>68.3557046979859</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -2607,50 +3051,78 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.079698169566351</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1511855864373501</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.03611021021182145</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.03611021021182145</v>
-      </c>
+        <v>1.211753542646572</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.03849785307221509</v>
+        <v>2.460427299563889</v>
       </c>
       <c r="E5" s="4">
-        <v>98.29931972789115</v>
+        <v>67.24489795918318</v>
       </c>
       <c r="F5" s="4">
-        <v>98.15436241610739</v>
+        <v>59.08277404921667</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.211753542646572</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3133,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3141,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3152,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3194,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,66 +3225,100 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1469231238309308</v>
+        <v>0.2507433826043168</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1242521951880702</v>
+        <v>0.2507433826043168</v>
       </c>
       <c r="D3" s="4">
-        <v>0.10288872255604</v>
+        <v>0.2440630132272374</v>
       </c>
       <c r="E3" s="4">
-        <v>93.60544217687074</v>
+        <v>97.65306122448979</v>
       </c>
       <c r="F3" s="4">
-        <v>90.13049962714396</v>
+        <v>97.76286353467563</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2507433826043168</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2507433826043168</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1607673818119265</v>
+        <v>0.1790981382473455</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1607673818119265</v>
+        <v>0.1790981382473455</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1590430244056567</v>
+        <v>0.1648009807213766</v>
       </c>
       <c r="E4" s="4">
-        <v>94.11564625850342</v>
+        <v>97.27891156462584</v>
       </c>
       <c r="F4" s="4">
-        <v>95.16778523489933</v>
+        <v>96.8903803131991</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -2820,50 +3341,82 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1790981382473455</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1790981382473455</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2526188329174956</v>
+        <v>0.1353772883012656</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2526188329174956</v>
+        <v>0.1394850668312415</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2517594232474488</v>
+        <v>0.08902871652385554</v>
       </c>
       <c r="E5" s="4">
-        <v>94.62585034013605</v>
+        <v>94.65986394557821</v>
       </c>
       <c r="F5" s="4">
-        <v>96.38702460850111</v>
+        <v>91.31991051454159</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1353772883012656</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1394850668312415</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3427,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3435,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3446,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3488,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,34 +3519,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4180833191021556</v>
+        <v>0.03611021021182145</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2455730246656511</v>
+        <v>0.03611021021182145</v>
       </c>
       <c r="D3" s="4">
-        <v>1.324714600080657</v>
+        <v>0.03849785307221509</v>
       </c>
       <c r="E3" s="4">
-        <v>89.45578231292519</v>
+        <v>98.29931972789115</v>
       </c>
       <c r="F3" s="4">
-        <v>78.45637583892467</v>
+        <v>98.15436241610739</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2992,34 +3578,50 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03611021021182145</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03611021021182145</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1782654610312188</v>
+        <v>0.399449711295644</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1703499827745105</v>
+        <v>0.399449711295644</v>
       </c>
       <c r="D4" s="4">
-        <v>1.390553532743058</v>
+        <v>0.3886784963336574</v>
       </c>
       <c r="E4" s="4">
-        <v>72.72108843537366</v>
+        <v>98.57142857142857</v>
       </c>
       <c r="F4" s="4">
-        <v>64.65324384787409</v>
+        <v>97.93064876957496</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -3033,50 +3635,82 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.399449711295644</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.399449711295644</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.229259438595641</v>
+        <v>0.3432535632843283</v>
       </c>
       <c r="C5" s="4">
-        <v>0.08410056929273857</v>
+        <v>0.179299953186316</v>
       </c>
       <c r="D5" s="4">
-        <v>1.226974798670817</v>
+        <v>0.7333429162099657</v>
       </c>
       <c r="E5" s="4">
-        <v>94.65986394557822</v>
+        <v>83.2879818594114</v>
       </c>
       <c r="F5" s="4">
-        <v>92.718120805369</v>
+        <v>76.2080536912743</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3432535632843283</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.179299953186316</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3721,1454 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2526188329174956</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2526188329174956</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2517594232474488</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.62585034013605</v>
+      </c>
+      <c r="F3" s="4">
+        <v>96.38702460850111</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2526188329174956</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2526188329174956</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1469231238309308</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1242521951880702</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.10288872255604</v>
+      </c>
+      <c r="E4" s="4">
+        <v>93.60544217687074</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.13049962714396</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1469231238309308</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1242521951880702</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1607673818119265</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1607673818119265</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1590430244056567</v>
+      </c>
+      <c r="E5" s="4">
+        <v>94.11564625850342</v>
+      </c>
+      <c r="F5" s="4">
+        <v>95.16778523489933</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1607673818119265</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1607673818119265</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.229259438595641</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.08410056929273857</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.226974798670817</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.65986394557822</v>
+      </c>
+      <c r="F3" s="4">
+        <v>92.718120805369</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.229259438595641</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08410056929273857</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4180833191021556</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2455730246656511</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.324714600080657</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.45578231292519</v>
+      </c>
+      <c r="F4" s="4">
+        <v>78.45637583892467</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4180833191021556</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2455730246656511</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1782654610312188</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1703499827745105</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.390553532743058</v>
+      </c>
+      <c r="E5" s="4">
+        <v>72.72108843537366</v>
+      </c>
+      <c r="F5" s="4">
+        <v>64.65324384787409</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1782654610312188</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1703499827745105</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>100</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="G3" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.951122603020243</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4">
+        <v>2.235760901902621</v>
+      </c>
+      <c r="K3" s="4">
+        <v>78.62055933484508</v>
+      </c>
+      <c r="L3" s="4">
+        <v>76.11981108625417</v>
+      </c>
+      <c r="M3" s="5">
+        <v>9</v>
+      </c>
+      <c r="N3" s="5">
+        <v>57908.70523452759</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.75379255346584</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="C4" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D4" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5786119213347168</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.7634261335279007</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.6753208548470866</v>
+      </c>
+      <c r="K4" s="4">
+        <v>78.68858654572956</v>
+      </c>
+      <c r="L4" s="4">
+        <v>75.68356947551349</v>
+      </c>
+      <c r="M4" s="5">
+        <v>9</v>
+      </c>
+      <c r="N4" s="5">
+        <v>66076.30968093872</v>
+      </c>
+      <c r="O4" s="4">
+        <v>44.37629931560693</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="G5" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1.907037117521718</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1.137628829153982</v>
+      </c>
+      <c r="J5" s="4">
+        <v>2.032468122400234</v>
+      </c>
+      <c r="K5" s="4">
+        <v>79.48601662887437</v>
+      </c>
+      <c r="L5" s="4">
+        <v>77.80263484961363</v>
+      </c>
+      <c r="M5" s="5">
+        <v>9</v>
+      </c>
+      <c r="N5" s="5">
+        <v>365087.5473022461</v>
+      </c>
+      <c r="O5" s="4">
+        <v>189.5573973531911</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="C6" s="3">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="D6" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.7894503451696235</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1.325499515501481</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1.021957838930474</v>
+      </c>
+      <c r="K6" s="4">
+        <v>78.27286470143622</v>
+      </c>
+      <c r="L6" s="4">
+        <v>74.49291573452469</v>
+      </c>
+      <c r="M6" s="5">
+        <v>9</v>
+      </c>
+      <c r="N6" s="5">
+        <v>135228.1744480133</v>
+      </c>
+      <c r="O6" s="4">
+        <v>91.24708127396309</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C7" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D7" s="3">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="E7" s="3">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.4944619676736895</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3638986836716261</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1.387354269161329</v>
+      </c>
+      <c r="K7" s="4">
+        <v>80.113378684807</v>
+      </c>
+      <c r="L7" s="4">
+        <v>78.54586129753761</v>
+      </c>
+      <c r="M7" s="5">
+        <v>9</v>
+      </c>
+      <c r="N7" s="5">
+        <v>896493.0973052979</v>
+      </c>
+      <c r="O7" s="4">
+        <v>152.7245480928957</v>
+      </c>
+      <c r="P7" s="5">
+        <v>5870</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="C8" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D8" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G8" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.286680099538967</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1.466535642661007</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.610161410603526</v>
+      </c>
+      <c r="K8" s="4">
+        <v>75.17006802721141</v>
+      </c>
+      <c r="L8" s="4">
+        <v>74.58240119314003</v>
+      </c>
+      <c r="M8" s="5">
+        <v>9</v>
+      </c>
+      <c r="N8" s="5">
+        <v>16840.98029136658</v>
+      </c>
+      <c r="O8" s="4">
+        <v>11.76867944889348</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D9" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7735537964779522</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.7915027537601418</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.8490678481272577</v>
+      </c>
+      <c r="K9" s="4">
+        <v>81.23582766439931</v>
+      </c>
+      <c r="L9" s="4">
+        <v>82.3601789709149</v>
+      </c>
+      <c r="M9" s="5">
+        <v>9</v>
+      </c>
+      <c r="N9" s="5">
+        <v>37335.88838577271</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.0932192518982</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2516149107960525</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3578417868310429</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2489854229528133</v>
+      </c>
+      <c r="K10" s="4">
+        <v>80.29478458049932</v>
+      </c>
+      <c r="L10" s="4">
+        <v>83.34079045488362</v>
+      </c>
+      <c r="M10" s="5">
+        <v>9</v>
+      </c>
+      <c r="N10" s="5">
+        <v>106778.3935070038</v>
+      </c>
+      <c r="O10" s="4">
+        <v>83.16074260670077</v>
+      </c>
+      <c r="P10" s="5">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="D11" s="3">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="G11" s="3">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="H11" s="4">
+        <v>2.07090570303909</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4">
+        <v>2.293910573983643</v>
+      </c>
+      <c r="K11" s="4">
+        <v>71.39455782312972</v>
+      </c>
+      <c r="L11" s="4">
+        <v>68.98831717623506</v>
+      </c>
+      <c r="M11" s="5">
+        <v>9</v>
+      </c>
+      <c r="N11" s="5">
+        <v>59599.14112091064</v>
+      </c>
+      <c r="O11" s="4">
+        <v>36.67639453594501</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="C12" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D12" s="3">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G12" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1.051005339116576</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1.037091530783982</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1.374556453093343</v>
+      </c>
+      <c r="K12" s="4">
+        <v>79.31972789115659</v>
+      </c>
+      <c r="L12" s="4">
+        <v>76.5535669898064</v>
+      </c>
+      <c r="M12" s="5">
+        <v>9</v>
+      </c>
+      <c r="N12" s="5">
+        <v>21849.54833984375</v>
+      </c>
+      <c r="O12" s="4">
+        <v>16.66632215091057</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="C13" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="D13" s="3">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="E13" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="F13" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G13" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1.43146773412607</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1511855864373501</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2.092955077089654</v>
+      </c>
+      <c r="K13" s="4">
+        <v>72.65306122448992</v>
+      </c>
+      <c r="L13" s="4">
+        <v>64.56375838926134</v>
+      </c>
+      <c r="M13" s="5">
+        <v>9</v>
+      </c>
+      <c r="N13" s="5">
+        <v>280634.331703186</v>
+      </c>
+      <c r="O13" s="4">
+        <v>72.30979945972328</v>
+      </c>
+      <c r="P13" s="5">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1884062697176426</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1960618370271837</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1659642368241565</v>
+      </c>
+      <c r="K14" s="4">
+        <v>96.53061224489795</v>
+      </c>
+      <c r="L14" s="4">
+        <v>95.3243847874723</v>
+      </c>
+      <c r="M14" s="5">
+        <v>9</v>
+      </c>
+      <c r="N14" s="5">
+        <v>124882.8270435333</v>
+      </c>
+      <c r="O14" s="4">
+        <v>193.6167861140052</v>
+      </c>
+      <c r="P14" s="5">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="E15" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="F15" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.259604494930598</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2122828168155304</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.3868397552052794</v>
+      </c>
+      <c r="K15" s="4">
+        <v>93.3862433862441</v>
+      </c>
+      <c r="L15" s="4">
+        <v>90.76435495898332</v>
+      </c>
+      <c r="M15" s="5">
+        <v>9</v>
+      </c>
+      <c r="N15" s="5">
+        <v>254178.2402992249</v>
+      </c>
+      <c r="O15" s="4">
+        <v>208.1721869772521</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1867697795201176</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1860828793205508</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1712303900697151</v>
+      </c>
+      <c r="K16" s="4">
+        <v>94.1156462585034</v>
+      </c>
+      <c r="L16" s="4">
+        <v>93.89510315684832</v>
+      </c>
+      <c r="M16" s="5">
+        <v>9</v>
+      </c>
+      <c r="N16" s="5">
+        <v>88963.75370025635</v>
+      </c>
+      <c r="O16" s="4">
+        <v>106.9275885820389</v>
+      </c>
+      <c r="P16" s="5">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="C17" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="D17" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.6085360729096716</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.165939434138258</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.314080977164844</v>
+      </c>
+      <c r="K17" s="4">
+        <v>85.61224489795958</v>
+      </c>
+      <c r="L17" s="4">
+        <v>78.60924683072275</v>
+      </c>
+      <c r="M17" s="5">
+        <v>9</v>
+      </c>
+      <c r="N17" s="5">
+        <v>202583.7965011597</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.7879584582884</v>
+      </c>
+      <c r="P17" s="5">
+        <v>2010</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3382,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -3646,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
         <v>3</v>
@@ -3847,9 +5923,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5">
+        <v>4</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>6</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>5</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>3</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>4</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>3</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>5</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6691,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6733,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,108 +6764,148 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>1.942129565707243</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>2.181115898918506</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.79818594104316</v>
+      </c>
+      <c r="F3" s="4">
+        <v>78.47874720358014</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.942129565707243</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>1.088759615766321</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
         <v>1.586199318118209</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>70.40816326530614</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>67.50932140193868</v>
       </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.088759615766321</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>2.822478627587164</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>2.939967488671149</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>81.65532879818591</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>82.37136465324419</v>
       </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.942129565707243</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2.181115898918506</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.79818594104316</v>
-      </c>
-      <c r="F5" s="4">
-        <v>78.47874720358014</v>
-      </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
@@ -4042,9 +6927,23 @@
       <c r="M5" s="5">
         <v>2</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.822478627587164</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +6954,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +6973,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7015,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,116 +7046,166 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.7351814443184898</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.9053556775397738</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7483815684233074</v>
+      </c>
+      <c r="E3" s="4">
+        <v>82.21088435374149</v>
+      </c>
+      <c r="F3" s="4">
+        <v>82.31543624161081</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7351814443184898</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9053556775397738</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.09581931862946173</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.1335902568425809</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.3231161478530946</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>80.73696145124711</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>79.27293064876973</v>
       </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09581931862946173</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1335902568425809</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.904835001056199</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>1.109402922189474</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.9544648482648578</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>73.11791383219926</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>65.46234153616604</v>
       </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7351814443184898</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.9053556775397738</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7483815684233074</v>
-      </c>
-      <c r="E5" s="4">
-        <v>82.21088435374149</v>
-      </c>
-      <c r="F5" s="4">
-        <v>82.31543624161081</v>
-      </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>1</v>
@@ -4255,9 +7219,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.904835001056199</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.109402922189474</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7248,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7267,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7309,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,108 +7340,152 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>2.724353107096249</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>2.454888401857412</v>
+      </c>
+      <c r="E3" s="4">
+        <v>74.93197278911531</v>
+      </c>
+      <c r="F3" s="4">
+        <v>77.50559284116368</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.724353107096249</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.5014361136527441</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>1.137628829153982</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>1.094295381841221</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>81.90476190476195</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>79.64205816554821</v>
       </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5014361136527441</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.137628829153982</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>2.495322131816162</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>2.548220583502067</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>81.62131519274372</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>76.26025354213282</v>
       </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2.724353107096249</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2.454888401857412</v>
-      </c>
-      <c r="E5" s="4">
-        <v>74.93197278911531</v>
-      </c>
-      <c r="F5" s="4">
-        <v>77.50559284116368</v>
-      </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
@@ -4468,9 +7507,23 @@
       <c r="M5" s="5">
         <v>2</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.495322131816162</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7534,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7553,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7595,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,108 +7626,158 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.9921013051583335</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.508988498881081</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.11050505780319</v>
+      </c>
+      <c r="E3" s="4">
+        <v>80.81632653061233</v>
+      </c>
+      <c r="F3" s="4">
+        <v>80.61521252796452</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9921013051583335</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.508988498881081</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.5806460423639995</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>1.432600533637014</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.8989040099950216</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>79.69387755102048</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>75.74944071588376</v>
       </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5806460423639995</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.432600533637014</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.7956036879865375</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>1.034909513986349</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>1.056464448993211</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>74.30839002267575</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>67.11409395973084</v>
       </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.9921013051583335</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.508988498881081</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.11050505780319</v>
-      </c>
-      <c r="E5" s="4">
-        <v>80.81632653061233</v>
-      </c>
-      <c r="F5" s="4">
-        <v>80.61521252796452</v>
-      </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
@@ -4681,9 +7799,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7956036879865375</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.034909513986349</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7828,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7847,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +7889,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,108 +7920,158 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.5942254585109671</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.538253788381553</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.599222454857227</v>
+      </c>
+      <c r="E3" s="4">
+        <v>81.57596371882111</v>
+      </c>
+      <c r="F3" s="4">
+        <v>77.68456375838775</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5942254585109671</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.538253788381553</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.3939787891977176</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.1599890334255178</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>1.175171330320154</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>79.30839002267548</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>78.48993288590455</v>
       </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3939787891977176</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1599890334255178</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.4951816553123838</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.3934532292078075</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>1.387669022306606</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>79.45578231292514</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>79.46308724832058</v>
       </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5942254585109671</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.538253788381553</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.599222454857227</v>
-      </c>
-      <c r="E5" s="4">
-        <v>81.57596371882111</v>
-      </c>
-      <c r="F5" s="4">
-        <v>77.68456375838775</v>
-      </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
@@ -4880,13 +8079,13 @@
         <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -4894,9 +8093,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4951816553123838</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3934532292078075</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8122,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.02878011010098</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.466535642661007</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.127230708956526</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.83673469387746</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.79865771812113</v>
-      </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.133222497243205</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.865614513915699</v>
-      </c>
-      <c r="E4" s="4">
-        <v>67.89115646258459</v>
-      </c>
-      <c r="F4" s="4">
-        <v>66.84563758389211</v>
-      </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.698037691272716</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.837639008938353</v>
-      </c>
-      <c r="E5" s="4">
-        <v>75.78231292516972</v>
-      </c>
-      <c r="F5" s="4">
-        <v>72.10290827740373</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5019201782815799</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.5461023853658844</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6223730591409549</v>
-      </c>
-      <c r="E3" s="4">
-        <v>84.08163265306128</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.89932885906029</v>
-      </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.9089950873700824</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.8595380671213206</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.011625702604457</v>
-      </c>
-      <c r="E4" s="4">
-        <v>76.25850340136061</v>
-      </c>
-      <c r="F4" s="4">
-        <v>73.926174496643</v>
-      </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.9097461237821941</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.9097461237821941</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.9132047826363608</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.36734693877551</v>
-      </c>
-      <c r="F5" s="4">
-        <v>88.25503355704694</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
